--- a/results/20260726_202759/detailed_results.xlsx
+++ b/results/20260726_202759/detailed_results.xlsx
@@ -2054,7 +2054,7 @@
     <col min="1" max="1" width="8.328125" customWidth="1"/>
     <col min="2" max="2" width="8.7265625" customWidth="1"/>
     <col min="3" max="3" width="25.515625" customWidth="1"/>
-    <col min="4" max="4" width="16.7578125" customWidth="1"/>
+    <col min="4" max="4" width="16.7578125" hidden="1" customWidth="1"/>
     <col min="5" max="5" width="8.203125" customWidth="1"/>
     <col min="6" max="6" width="7.75" style="2" customWidth="1"/>
     <col min="7" max="7" width="9.2421875" customWidth="1"/>
@@ -2066,7 +2066,7 @@
     <col min="14" max="14" width="10.796875" customWidth="1"/>
     <col min="15" max="15" width="10.5"/>
     <col min="16" max="16" width="41.9296875" customWidth="1"/>
-    <col min="17" max="17" width="35.046875" style="3" customWidth="1"/>
+    <col min="17" max="17" width="35.046875" style="3" hidden="1" customWidth="1"/>
     <col min="18" max="18" width="9" style="2"/>
     <col min="20" max="20" width="9.6953125" style="2" customWidth="1"/>
     <col min="21" max="21" width="23.6796875" style="4" customWidth="1"/>
